--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -454,23 +454,28 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>16.56279</v>
+        <v>16.5879</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63879</v>
+        <v>15.67821</v>
       </c>
       <c r="E2" t="n">
-        <v>17.147</v>
+        <v>16.50782</v>
       </c>
       <c r="F2" t="n">
-        <v>42.71803</v>
+        <v>21.51611</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05154</v>
+        <v>21.37392</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84621</v>
+        <v>33.96896</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.89609</v>
+        <v>16.54198</v>
       </c>
       <c r="D3" t="n">
-        <v>16.45812</v>
+        <v>16.26079</v>
       </c>
       <c r="E3" t="n">
-        <v>16.68227</v>
+        <v>16.37857</v>
       </c>
       <c r="F3" t="n">
-        <v>42.88742</v>
+        <v>21.93905</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05117</v>
+        <v>21.7923</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84948</v>
+        <v>33.59972</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.96235</v>
+        <v>16.94435</v>
       </c>
       <c r="D4" t="n">
-        <v>16.40208</v>
+        <v>15.9748</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77628</v>
+        <v>16.59544</v>
       </c>
       <c r="F4" t="n">
-        <v>43.10324</v>
+        <v>21.80822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05058</v>
+        <v>21.59018</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85343</v>
+        <v>34.07712</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.39383</v>
+        <v>16.71228</v>
       </c>
       <c r="D5" t="n">
-        <v>16.67973</v>
+        <v>15.90097</v>
       </c>
       <c r="E5" t="n">
-        <v>16.99393</v>
+        <v>16.20054</v>
       </c>
       <c r="F5" t="n">
-        <v>42.42447</v>
+        <v>22.08663</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05099</v>
+        <v>21.9301</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81758</v>
+        <v>33.90889</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.5159</v>
+        <v>16.79288</v>
       </c>
       <c r="D6" t="n">
-        <v>16.40902</v>
+        <v>16.07198</v>
       </c>
       <c r="E6" t="n">
-        <v>16.81262</v>
+        <v>16.57797</v>
       </c>
       <c r="F6" t="n">
-        <v>43.22344</v>
+        <v>22.12951</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05017</v>
+        <v>21.83264</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88139</v>
+        <v>34.26807</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.96714</v>
+        <v>16.76153</v>
       </c>
       <c r="D7" t="n">
-        <v>16.38259</v>
+        <v>16.02205</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6852</v>
+        <v>16.35356</v>
       </c>
       <c r="F7" t="n">
-        <v>41.84855</v>
+        <v>21.85663</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05086</v>
+        <v>22.2529</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8132</v>
+        <v>34.25413</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.07602</v>
+        <v>16.83486</v>
       </c>
       <c r="D8" t="n">
-        <v>16.55116</v>
+        <v>15.75937</v>
       </c>
       <c r="E8" t="n">
-        <v>16.65013</v>
+        <v>16.71745</v>
       </c>
       <c r="F8" t="n">
-        <v>42.48493</v>
+        <v>21.55786</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05021</v>
+        <v>21.82461</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81815</v>
+        <v>34.42509</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.76453</v>
+        <v>16.67948</v>
       </c>
       <c r="D9" t="n">
-        <v>16.58424</v>
+        <v>15.80106</v>
       </c>
       <c r="E9" t="n">
-        <v>16.63941</v>
+        <v>16.66169</v>
       </c>
       <c r="F9" t="n">
-        <v>42.85504</v>
+        <v>21.67445</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05104</v>
+        <v>21.2263</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7991</v>
+        <v>34.0938</v>
       </c>
     </row>
     <row r="10">
@@ -655,284 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.72415</v>
+        <v>16.92314</v>
       </c>
       <c r="D10" t="n">
-        <v>16.43624</v>
+        <v>16.05766</v>
       </c>
       <c r="E10" t="n">
-        <v>16.5945</v>
+        <v>16.55152</v>
       </c>
       <c r="F10" t="n">
-        <v>42.77141</v>
+        <v>21.6446</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05066</v>
+        <v>21.80576</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81361</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>16.69519</v>
-      </c>
-      <c r="D12" t="n">
-        <v>16.5028</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.68017</v>
-      </c>
-      <c r="F12" t="n">
-        <v>42.6323</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05062</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.82383</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>17.07445</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.6242</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.69727</v>
-      </c>
-      <c r="F13" t="n">
-        <v>42.321</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05027</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.83983</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>16.77228</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16.61963</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.66709</v>
-      </c>
-      <c r="F14" t="n">
-        <v>42.30549</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05087</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.82701</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>17.05355</v>
-      </c>
-      <c r="D15" t="n">
-        <v>16.37851</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.70124</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.44609</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05087</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.82656</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>16.79283</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16.66519</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.66447</v>
-      </c>
-      <c r="F16" t="n">
-        <v>42.82608</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05065</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.83822</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>16.77665</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16.52618</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.41341</v>
-      </c>
-      <c r="F17" t="n">
-        <v>41.51055</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.80001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>16.9058</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16.56147</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.88632</v>
-      </c>
-      <c r="F18" t="n">
-        <v>42.42409</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.0508</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.81608</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>16.62451</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.46345</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.88214</v>
-      </c>
-      <c r="F19" t="n">
-        <v>41.96216</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05138</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.82332</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>16.94035</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.70573</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.61167</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.38815</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05027</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.82815</v>
+        <v>34.12297</v>
       </c>
     </row>
   </sheetData>
